--- a/data/trans_orig/IP2903-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP2903-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31975</t>
+          <t>31620</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49025</t>
+          <t>49157</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38267</t>
+          <t>38978</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56860</t>
+          <t>57957</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74988</t>
+          <t>74400</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101019</t>
+          <t>102169</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,71%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29134</t>
+          <t>28584</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45546</t>
+          <t>44742</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26230</t>
+          <t>26215</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42224</t>
+          <t>42667</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58764</t>
+          <t>58859</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>82532</t>
+          <t>82252</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,56%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47281</t>
+          <t>47283</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67021</t>
+          <t>65908</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>54333</t>
+          <t>53706</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>72340</t>
+          <t>73466</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>105922</t>
+          <t>105268</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>131861</t>
+          <t>133201</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,86%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>51437</t>
+          <t>51313</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>71463</t>
+          <t>71209</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64440</t>
+          <t>64099</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>86522</t>
+          <t>85669</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>121218</t>
+          <t>120154</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>151223</t>
+          <t>151498</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,99%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30501</t>
+          <t>30549</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47833</t>
+          <t>48118</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37984</t>
+          <t>38468</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>58044</t>
+          <t>57331</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>72861</t>
+          <t>72887</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>99030</t>
+          <t>98662</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79051</t>
+          <t>79903</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>100334</t>
+          <t>100894</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74606</t>
+          <t>75732</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>96905</t>
+          <t>98747</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>161017</t>
+          <t>161578</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>192175</t>
+          <t>192097</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,17%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38468</t>
+          <t>38524</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>54950</t>
+          <t>55636</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33941</t>
+          <t>34738</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52068</t>
+          <t>51966</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>77431</t>
+          <t>76944</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>102160</t>
+          <t>101655</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,1%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20262</t>
+          <t>20413</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34920</t>
+          <t>35105</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31832</t>
+          <t>31141</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48673</t>
+          <t>48691</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55383</t>
+          <t>55758</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77869</t>
+          <t>77609</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,56%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54146</t>
+          <t>54364</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>72385</t>
+          <t>72106</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52571</t>
+          <t>53625</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71810</t>
+          <t>72000</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>111813</t>
+          <t>114145</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>138373</t>
+          <t>139879</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,67%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54418</t>
+          <t>54620</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>77799</t>
+          <t>77249</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50992</t>
+          <t>49677</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71005</t>
+          <t>70740</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>110584</t>
+          <t>110917</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>142079</t>
+          <t>141502</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,97%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24074</t>
+          <t>25126</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42497</t>
+          <t>42150</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34803</t>
+          <t>34205</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53122</t>
+          <t>53126</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>62540</t>
+          <t>62684</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>88529</t>
+          <t>88988</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>86375</t>
+          <t>86250</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>109920</t>
+          <t>110870</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>81196</t>
+          <t>82370</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>103277</t>
+          <t>104917</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>176471</t>
+          <t>177337</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>209872</t>
+          <t>209218</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,18%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>194118</t>
+          <t>192578</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>232729</t>
+          <t>231965</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>207014</t>
+          <t>205974</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>244556</t>
+          <t>246058</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>413238</t>
+          <t>412482</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>466694</t>
+          <t>467301</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,56%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>118186</t>
+          <t>118225</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>151356</t>
+          <t>150886</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>146354</t>
+          <t>149018</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>181472</t>
+          <t>183634</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>272867</t>
+          <t>273024</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>322976</t>
+          <t>323325</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>289042</t>
+          <t>288312</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>330723</t>
+          <t>328554</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>285120</t>
+          <t>285452</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>327311</t>
+          <t>326420</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>586863</t>
+          <t>585398</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>644251</t>
+          <t>646879</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>47,84%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33700</t>
+          <t>33447</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52414</t>
+          <t>53318</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37923</t>
+          <t>36972</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56623</t>
+          <t>56413</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>76556</t>
+          <t>78017</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>103976</t>
+          <t>104534</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,62%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12279</t>
+          <t>12644</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25819</t>
+          <t>26236</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23719</t>
+          <t>23361</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40352</t>
+          <t>39695</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39924</t>
+          <t>39663</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60871</t>
+          <t>60591</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66117</t>
+          <t>64495</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>85933</t>
+          <t>85303</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61333</t>
+          <t>59996</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>80672</t>
+          <t>81048</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>131324</t>
+          <t>131135</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>159935</t>
+          <t>158339</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>55,47%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67836</t>
+          <t>67545</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88555</t>
+          <t>88793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73203</t>
+          <t>72705</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>96100</t>
+          <t>97033</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>148406</t>
+          <t>147117</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>179466</t>
+          <t>179178</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,91%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25323</t>
+          <t>25403</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40998</t>
+          <t>42834</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37706</t>
+          <t>36924</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57940</t>
+          <t>57927</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>67580</t>
+          <t>66924</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>93667</t>
+          <t>94596</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78926</t>
+          <t>78402</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>100477</t>
+          <t>100226</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74440</t>
+          <t>73666</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97356</t>
+          <t>97463</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>160011</t>
+          <t>158773</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>191883</t>
+          <t>191493</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>45,86%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48808</t>
+          <t>49798</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68369</t>
+          <t>68412</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51355</t>
+          <t>50421</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71358</t>
+          <t>70096</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>106514</t>
+          <t>105675</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>132663</t>
+          <t>132639</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21498</t>
+          <t>21540</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36613</t>
+          <t>37127</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23821</t>
+          <t>24019</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39633</t>
+          <t>40169</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48577</t>
+          <t>49280</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70943</t>
+          <t>70575</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,32%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>55784</t>
+          <t>55981</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74934</t>
+          <t>75094</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61472</t>
+          <t>62277</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82797</t>
+          <t>82622</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>122945</t>
+          <t>122992</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>152287</t>
+          <t>151131</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>47,81%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68803</t>
+          <t>67536</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>93324</t>
+          <t>91897</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>74467</t>
+          <t>74276</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>99078</t>
+          <t>98132</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>149042</t>
+          <t>149071</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>181875</t>
+          <t>182865</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,27%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31931</t>
+          <t>31876</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51134</t>
+          <t>51485</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35816</t>
+          <t>36516</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57452</t>
+          <t>56615</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>74388</t>
+          <t>72800</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>101937</t>
+          <t>101046</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>73530</t>
+          <t>75253</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>98824</t>
+          <t>99523</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>61768</t>
+          <t>61420</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>84422</t>
+          <t>84253</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>143715</t>
+          <t>145459</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>178752</t>
+          <t>177779</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,04%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>240259</t>
+          <t>239779</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>281544</t>
+          <t>280987</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>256083</t>
+          <t>255816</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>298709</t>
+          <t>299894</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>507907</t>
+          <t>506417</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>566039</t>
+          <t>568078</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,66%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>104329</t>
+          <t>105783</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>137504</t>
+          <t>138761</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>136464</t>
+          <t>137938</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>173196</t>
+          <t>171904</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>251068</t>
+          <t>250916</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>298973</t>
+          <t>300625</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>297192</t>
+          <t>294882</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>338627</t>
+          <t>338753</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>280659</t>
+          <t>279708</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>324636</t>
+          <t>323832</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>586847</t>
+          <t>588357</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>648379</t>
+          <t>650487</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,42%</t>
         </is>
       </c>
     </row>
@@ -5756,12 +5756,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30632</t>
+          <t>30851</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48080</t>
+          <t>47963</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29618</t>
+          <t>28915</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48174</t>
+          <t>47261</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63709</t>
+          <t>63921</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89437</t>
+          <t>88909</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22608</t>
+          <t>22085</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38623</t>
+          <t>38496</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29293</t>
+          <t>28769</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47650</t>
+          <t>46419</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54265</t>
+          <t>54527</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>79318</t>
+          <t>77771</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,42%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51669</t>
+          <t>52139</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>70305</t>
+          <t>70872</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59253</t>
+          <t>58552</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79489</t>
+          <t>79344</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116273</t>
+          <t>117040</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>145485</t>
+          <t>144840</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>52,93%</t>
         </is>
       </c>
     </row>
@@ -6212,12 +6212,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48895</t>
+          <t>48653</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69420</t>
+          <t>68383</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>55988</t>
+          <t>56132</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>77485</t>
+          <t>77433</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>111021</t>
+          <t>110168</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>139878</t>
+          <t>138725</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,85%</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48717</t>
+          <t>48685</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67273</t>
+          <t>68913</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48917</t>
+          <t>48733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>70524</t>
+          <t>69820</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>102762</t>
+          <t>102095</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>132134</t>
+          <t>130142</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>30,81%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76258</t>
+          <t>76780</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98282</t>
+          <t>98427</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>81353</t>
+          <t>82493</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104046</t>
+          <t>106044</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>164343</t>
+          <t>166170</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>196569</t>
+          <t>198077</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,9%</t>
         </is>
       </c>
     </row>
@@ -6668,12 +6668,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37899</t>
+          <t>37273</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55846</t>
+          <t>54940</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41632</t>
+          <t>41896</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60993</t>
+          <t>60525</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>83401</t>
+          <t>84546</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>110409</t>
+          <t>108501</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,43%</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38914</t>
+          <t>39591</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57425</t>
+          <t>57056</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42760</t>
+          <t>42387</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60686</t>
+          <t>62524</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>86861</t>
+          <t>87413</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>112601</t>
+          <t>112805</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,8%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49200</t>
+          <t>50338</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68493</t>
+          <t>68839</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50787</t>
+          <t>49882</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69455</t>
+          <t>71121</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>105100</t>
+          <t>104259</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>132054</t>
+          <t>132178</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,95%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39734</t>
+          <t>39926</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60137</t>
+          <t>60798</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37086</t>
+          <t>37424</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58245</t>
+          <t>56527</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81748</t>
+          <t>83833</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>110996</t>
+          <t>113138</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,26%</t>
         </is>
       </c>
     </row>
@@ -7237,12 +7237,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54366</t>
+          <t>53537</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>75661</t>
+          <t>75662</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39971</t>
+          <t>40491</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>61224</t>
+          <t>61151</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>99960</t>
+          <t>99096</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>131443</t>
+          <t>130052</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7350,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>76153</t>
+          <t>77104</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>99282</t>
+          <t>99773</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>90400</t>
+          <t>89419</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>114639</t>
+          <t>112065</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>172877</t>
+          <t>171360</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>206379</t>
+          <t>206508</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,58%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>174185</t>
+          <t>175191</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>213377</t>
+          <t>213686</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>181207</t>
+          <t>180200</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>219387</t>
+          <t>220090</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>366362</t>
+          <t>367262</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>422108</t>
+          <t>422653</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,94%</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>180502</t>
+          <t>179875</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>219455</t>
+          <t>218700</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>176142</t>
+          <t>180249</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>216724</t>
+          <t>218865</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>368828</t>
+          <t>366803</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>426157</t>
+          <t>425607</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,15%</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>275301</t>
+          <t>273762</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>315692</t>
+          <t>317065</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>304196</t>
+          <t>303314</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>347574</t>
+          <t>346567</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>590268</t>
+          <t>589484</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>652471</t>
+          <t>650447</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2903-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP2903-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>47933</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>39240</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>57244</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>32,9%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>26,93%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>39,29%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>39926</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>31620</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>49157</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>31710</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>48767</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>30,11%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>23,85%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>37,07%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>47933</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>38978</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>57957</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>32,9%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74400</t>
+          <t>76126</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102169</t>
+          <t>100179</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,0%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>34272</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>26400</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>42818</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>23,52%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>18,12%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>29,39%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>36237</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>28584</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>44742</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>28377</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>44462</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>27,33%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>21,56%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>33,74%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>34272</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>26215</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>42667</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>23,52%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58859</t>
+          <t>59114</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>82252</t>
+          <t>83208</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,9%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>63488</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>54054</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>72728</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>43,58%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>37,1%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>49,92%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>56440</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>47283</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>65908</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>47833</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>66587</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>42,56%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>35,66%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>49,7%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>63488</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>53706</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>73466</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>43,58%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>105268</t>
+          <t>107288</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>133201</t>
+          <t>133394</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>47,93%</t>
         </is>
       </c>
     </row>
@@ -1061,57 +1061,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>145693</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>145693</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>145693</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>194</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>132603</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>132603</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>132603</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>145693</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>145693</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>145693</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>74833</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>64389</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>85498</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>35,85%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>30,85%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>40,96%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>61544</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>51313</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>71209</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>52254</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>72608</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>32,38%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>27,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>37,47%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>74833</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>64099</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>85669</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>35,85%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>120154</t>
+          <t>121369</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>151498</t>
+          <t>150651</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>37,78%</t>
         </is>
       </c>
     </row>
@@ -1291,72 +1291,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47657</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>38232</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>57359</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>22,83%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>18,32%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>27,48%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>38135</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>30549</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>48118</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>29957</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>47323</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>20,07%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>16,07%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>25,32%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>47657</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>38468</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>57331</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>22,83%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>72887</t>
+          <t>72700</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>98662</t>
+          <t>98734</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>86222</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>74531</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>97556</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>41,31%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>35,71%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>46,74%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>90366</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>79903</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>100894</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>80349</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>101386</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>47,55%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>42,04%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>53,09%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>86222</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>75732</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>98747</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>41,31%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>161578</t>
+          <t>160101</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>192097</t>
+          <t>191431</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,01%</t>
         </is>
       </c>
     </row>
@@ -1517,57 +1517,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>208713</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>208713</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>208713</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>304</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>190045</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>190045</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>190045</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>208713</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>208713</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>208713</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1634,72 +1634,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>43040</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35019</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>51317</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>29,69%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>24,15%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>35,39%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>46247</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>38524</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55636</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>38332</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>54553</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>33,85%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>28,2%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>40,72%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>43040</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>34738</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>51966</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>29,69%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>76944</t>
+          <t>77399</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>101655</t>
+          <t>102872</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,53%</t>
         </is>
       </c>
     </row>
@@ -1747,72 +1747,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>39733</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>31562</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>48592</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>27,4%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>21,77%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>33,51%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>26924</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>20413</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>35105</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>19875</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>33922</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>19,71%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>14,94%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>25,7%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>39733</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>31141</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>48691</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>27,4%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55758</t>
+          <t>55257</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77609</t>
+          <t>78108</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -1860,72 +1860,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>62216</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>52890</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>71869</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>42,91%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>36,48%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>49,57%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>63443</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>54364</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>72106</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>54568</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>72412</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>46,44%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>39,79%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>52,78%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>62216</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>53625</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>72000</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>42,91%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>114145</t>
+          <t>112321</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>139879</t>
+          <t>139196</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>49,43%</t>
         </is>
       </c>
     </row>
@@ -1973,57 +1973,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>144990</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>144990</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>144990</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>136614</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>136614</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>136614</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>144990</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>144990</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>144990</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2090,72 +2090,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>60214</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>49220</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>71467</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>30,65%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>25,05%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>36,37%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>65484</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>54620</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>77249</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>53532</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>76982</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>33,25%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>27,73%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>39,22%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>60214</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>49677</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>70740</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>30,65%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>110917</t>
+          <t>111289</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>141502</t>
+          <t>140952</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,83%</t>
         </is>
       </c>
     </row>
@@ -2203,72 +2203,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>42934</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>33159</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>52823</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>21,85%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>16,88%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>26,89%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>32454</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>25126</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>42150</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>25202</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>42279</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>16,48%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>12,76%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>21,4%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>42934</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>34205</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>53126</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>21,85%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>62684</t>
+          <t>63281</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>88988</t>
+          <t>89644</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,79%</t>
         </is>
       </c>
     </row>
@@ -2316,72 +2316,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>93325</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>81937</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>105526</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>47,5%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>41,7%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>53,71%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>99006</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>86250</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>110870</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>86791</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>111104</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>50,27%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>43,79%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>56,3%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>93325</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>82370</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>104917</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>47,5%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>177337</t>
+          <t>175897</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>209218</t>
+          <t>208826</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>53,08%</t>
         </is>
       </c>
     </row>
@@ -2429,57 +2429,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>196474</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>196474</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>196474</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>196944</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>196944</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>196944</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>196474</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>196474</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>196474</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2546,107 +2546,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>226021</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>207445</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>248588</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>32,48%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>29,81%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>35,72%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>321</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>213200</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>192578</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>231965</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>193917</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>234849</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>32,49%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>29,35%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>35,35%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>226021</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>205974</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>246058</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>29,55%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>35,79%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>439222</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>413412</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>467735</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>32,48%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>29,6%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>35,36%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>662</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>439222</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>412482</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>467301</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>32,48%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,59%</t>
         </is>
       </c>
     </row>
@@ -2659,72 +2659,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>164597</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>146003</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>182241</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>23,65%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>20,98%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>26,19%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>133750</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>118225</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>150886</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>117719</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>151000</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>20,38%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>18,02%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>22,99%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>164597</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>149018</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>183634</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>23,65%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>273024</t>
+          <t>276086</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>323325</t>
+          <t>324587</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -2772,72 +2772,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>305253</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>283044</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>324302</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>43,87%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>40,67%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>46,6%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>459</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>309256</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>288312</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>328554</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>289545</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>331134</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>47,13%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>43,94%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>50,07%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>460</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>305253</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>285452</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>326420</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>43,87%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>585398</t>
+          <t>586359</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>646879</t>
+          <t>641183</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,42%</t>
         </is>
       </c>
     </row>
@@ -2885,57 +2885,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>695871</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>695871</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>695871</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>982</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>656206</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>656206</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>656206</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1047</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>695871</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>695871</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>695871</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3055,7 +3055,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3066,7 +3066,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>46760</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>37544</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>58133</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>31,53%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>25,31%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>39,2%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>43058</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>33447</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>53318</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>33622</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>52778</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>31,4%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>24,39%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>38,89%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>46760</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>36972</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>56413</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>31,53%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78017</t>
+          <t>76922</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>104534</t>
+          <t>102612</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>35,95%</t>
         </is>
       </c>
     </row>
@@ -3347,72 +3347,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>30854</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>23117</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>40431</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>20,8%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>15,59%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>27,26%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18811</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12644</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>26236</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>12543</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>26397</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>13,72%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>9,22%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>19,13%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>30854</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>23361</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>39695</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>20,8%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39663</t>
+          <t>40184</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60591</t>
+          <t>61625</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -3460,72 +3460,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>70698</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60037</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>80961</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>47,67%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>40,48%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>54,59%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>75244</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>64495</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>85303</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>65560</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>85079</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>54,88%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>47,04%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>62,21%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>70698</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>59996</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>81048</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>47,67%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>131135</t>
+          <t>132445</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>158339</t>
+          <t>159874</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>56,01%</t>
         </is>
       </c>
     </row>
@@ -3573,57 +3573,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>148313</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>148313</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>148313</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>137113</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>137113</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>137113</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>148313</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>148313</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>148313</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3690,72 +3690,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>84286</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>72902</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>95826</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>38,82%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>33,58%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>44,14%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>78383</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>67545</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>88793</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>68065</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>89866</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>39,1%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>33,69%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>44,29%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>84286</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>72705</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>97033</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>38,82%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>147117</t>
+          <t>147640</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>179178</t>
+          <t>179313</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,94%</t>
         </is>
       </c>
     </row>
@@ -3803,72 +3803,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47492</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>37925</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>58204</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>21,87%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>17,47%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>26,81%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>32814</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>25403</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>42834</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>24888</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>40999</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>16,37%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>12,67%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>21,37%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>47492</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>36924</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>57927</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>21,87%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>66924</t>
+          <t>67496</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>94596</t>
+          <t>93498</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -3916,72 +3916,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>85338</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>73228</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>97120</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>39,31%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>33,73%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>44,73%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>89287</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>78402</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>100226</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>78163</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>100864</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>44,54%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>39,11%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>49,99%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>85338</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>73666</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>97463</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>39,31%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>158773</t>
+          <t>156451</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>191493</t>
+          <t>191998</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>45,98%</t>
         </is>
       </c>
     </row>
@@ -4029,57 +4029,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>217117</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>217117</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>217117</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>310</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>200483</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>200483</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>200483</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>217117</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>217117</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>217117</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4146,72 +4146,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>60553</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70414</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>36,88%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>30,78%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>42,88%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>58461</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>49798</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>68412</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>49215</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>68529</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>38,48%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>32,78%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>45,03%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>60553</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>50421</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>70096</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>36,88%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>105675</t>
+          <t>105717</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>132639</t>
+          <t>132577</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,94%</t>
         </is>
       </c>
     </row>
@@ -4259,72 +4259,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>31332</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24434</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>41117</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>19,08%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14,88%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>25,04%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>28432</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>21540</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>37127</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>21253</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>36424</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>18,71%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>14,18%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>24,44%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>31332</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>24019</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>40169</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>19,08%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49280</t>
+          <t>49182</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70575</t>
+          <t>70030</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -4372,72 +4372,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>72318</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>61931</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>82537</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>44,04%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>37,72%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>50,27%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>65033</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>55981</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>75094</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>55654</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>74573</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>42,81%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>36,85%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>49,43%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>72318</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>62277</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>82622</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>44,04%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>122992</t>
+          <t>123431</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>151131</t>
+          <t>151275</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,85%</t>
         </is>
       </c>
     </row>
@@ -4485,57 +4485,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>164203</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>164203</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>164203</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>151926</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>151926</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>151926</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>164203</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>164203</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>164203</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4602,72 +4602,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>85934</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>75762</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>99137</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>41,92%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>36,96%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>48,36%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>79806</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>67536</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>91897</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>68267</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>91057</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>38,35%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>32,46%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>44,16%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>85934</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>74276</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>98132</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>41,92%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>149071</t>
+          <t>148275</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>182865</t>
+          <t>183262</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,36%</t>
         </is>
       </c>
     </row>
@@ -4715,72 +4715,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>45738</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>36406</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>56489</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>22,31%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>17,76%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>27,55%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>41168</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>31876</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>51485</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>32184</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>52562</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>19,78%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>15,32%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>24,74%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>45738</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>36516</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>56615</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>22,31%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>72800</t>
+          <t>74095</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>101046</t>
+          <t>102747</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -4828,72 +4828,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>73335</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>62232</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>84924</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>35,77%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>30,36%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>41,42%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>87110</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>75253</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>99523</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>75309</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>99640</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>41,86%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>36,16%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>47,83%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>73335</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>61420</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>84253</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>35,77%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>145459</t>
+          <t>144020</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>177779</t>
+          <t>177629</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,0%</t>
         </is>
       </c>
     </row>
@@ -4941,57 +4941,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>205007</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>205007</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>205007</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>208084</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>208084</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>208084</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>205007</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>205007</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>205007</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5058,72 +5058,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>277534</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>256798</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>301394</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>37,78%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>34,96%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>41,03%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>378</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>259708</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>239779</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>280987</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>240508</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>281654</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>37,23%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>34,37%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>40,28%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>277534</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>255816</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>299894</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>37,78%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>506417</t>
+          <t>504958</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>568078</t>
+          <t>566354</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -5171,72 +5171,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>155416</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>138390</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>173718</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>21,16%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>18,84%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>23,65%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>121224</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>105783</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>138761</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>105901</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>141081</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>17,38%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>15,16%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>19,89%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>155416</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>137938</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>171904</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>21,16%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>250916</t>
+          <t>252306</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>300625</t>
+          <t>301264</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -5284,72 +5284,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>301690</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>280353</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>323791</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>41,07%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>38,16%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>44,07%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>453</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>316674</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>294882</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>338753</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>291129</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>336944</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>45,39%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>42,27%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>48,56%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>424</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>301690</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>279708</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>323832</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>41,07%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>588357</t>
+          <t>588712</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>650487</t>
+          <t>651701</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,5%</t>
         </is>
       </c>
     </row>
@@ -5397,57 +5397,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1049</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>734641</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>734641</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>734641</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1005</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>697606</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>697606</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>697606</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1049</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>734641</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>734641</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>734641</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5578,7 +5578,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5746,72 +5746,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>37573</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>28721</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>47153</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>26,06%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>19,92%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>32,7%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>38910</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>30851</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>47963</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>30903</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>48581</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>30,05%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>23,83%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>37,04%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>37573</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>28915</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>47261</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>26,06%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63921</t>
+          <t>64857</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88909</t>
+          <t>89267</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -5859,72 +5859,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>37244</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>28312</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>47286</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>25,83%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>19,64%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>32,79%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>29523</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>22085</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>38496</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>22257</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>37456</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>22,8%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>17,06%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>29,73%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>37244</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>28769</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>46419</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>25,83%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54527</t>
+          <t>54129</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>77771</t>
+          <t>79082</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -5972,72 +5972,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>69372</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>59001</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>80200</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>48,11%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>40,92%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>55,62%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>61042</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>52139</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>70872</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>51763</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>70642</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>47,15%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>40,27%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>54,74%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>69372</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>58552</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>79344</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>48,11%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>117040</t>
+          <t>117191</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>144840</t>
+          <t>145372</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>53,12%</t>
         </is>
       </c>
     </row>
@@ -6085,57 +6085,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>144190</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>144190</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>144190</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>129475</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>129475</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>129475</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>144190</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>144190</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>144190</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6202,72 +6202,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>66110</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>55636</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>78711</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>30,17%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>25,39%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>35,92%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>58458</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>48653</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>68383</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>49416</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>69360</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>28,76%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>23,94%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>33,65%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>66110</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>56132</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>77433</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>30,17%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>110168</t>
+          <t>110517</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>138725</t>
+          <t>138673</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,83%</t>
         </is>
       </c>
     </row>
@@ -6315,72 +6315,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>59142</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>48730</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>69299</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>26,99%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>22,24%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>31,62%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>57610</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>48685</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>68913</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>48440</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>67861</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>28,35%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>23,96%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>33,91%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>59142</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>48733</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>69820</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>26,99%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>102095</t>
+          <t>102747</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>130142</t>
+          <t>131887</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,23%</t>
         </is>
       </c>
     </row>
@@ -6428,72 +6428,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>93876</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>81802</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>105710</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>42,84%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>37,33%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>48,24%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>87161</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>76780</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>98427</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>76312</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>98064</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>42,89%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>37,78%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>48,43%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>93876</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>82493</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>106044</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>42,84%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>166170</t>
+          <t>165618</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>198077</t>
+          <t>196952</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,63%</t>
         </is>
       </c>
     </row>
@@ -6541,57 +6541,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>219129</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>219129</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>219129</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>327</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>203228</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>203228</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>203228</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>219129</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>219129</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>219129</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6663,67 +6663,67 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>50323</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>40969</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>59747</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>31,04%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>25,27%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>36,86%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>46338</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>37273</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>54940</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>37355</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>55202</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>30,29%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>24,36%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>35,91%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>50323</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>41896</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>60525</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>31,04%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>84546</t>
+          <t>83644</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>108501</t>
+          <t>110165</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,96%</t>
         </is>
       </c>
     </row>
@@ -6776,67 +6776,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>51683</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>42456</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>61404</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>31,88%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>26,19%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>37,88%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>47449</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>39591</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>57056</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>39871</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>56322</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>31,01%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>25,88%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>37,29%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>51683</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>42387</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>62524</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>31,88%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87413</t>
+          <t>85723</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>112805</t>
+          <t>112158</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,59%</t>
         </is>
       </c>
     </row>
@@ -6884,72 +6884,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>60105</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>50563</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>70808</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>37,08%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>31,19%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>43,68%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>59202</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>50338</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>68839</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>50187</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>69399</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>38,7%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>32,9%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>45,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>60105</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>49882</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>71121</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>37,08%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>104259</t>
+          <t>104948</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>132178</t>
+          <t>133555</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,38%</t>
         </is>
       </c>
     </row>
@@ -6997,57 +6997,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>162111</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>162111</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>162111</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>152989</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>152989</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>152989</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>162111</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>162111</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>162111</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7114,72 +7114,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>46545</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>36217</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>57213</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>23,51%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>18,29%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>28,9%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>49872</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>39926</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>60798</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>38872</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>60454</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>24,64%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>19,73%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>30,04%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>46545</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>37424</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>56527</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>23,51%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83833</t>
+          <t>81768</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>113138</t>
+          <t>111823</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -7227,72 +7227,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>50139</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>40262</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>60717</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>25,33%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>20,34%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>30,67%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>64477</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>53537</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>75662</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>53272</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>75563</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>31,86%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>26,45%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>37,39%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>50139</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>40491</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>61151</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>25,33%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>99096</t>
+          <t>97488</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>130052</t>
+          <t>128691</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,15%</t>
         </is>
       </c>
     </row>
@@ -7340,72 +7340,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>101281</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>89599</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>113279</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>51,16%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>45,26%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>57,22%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>88020</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>77104</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>99773</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>76373</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>100133</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>43,49%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>38,1%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>49,3%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>101281</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>89419</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>112065</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>51,16%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>171360</t>
+          <t>173430</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>206508</t>
+          <t>206364</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,55%</t>
         </is>
       </c>
     </row>
@@ -7453,57 +7453,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>197965</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>197965</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>197965</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>202369</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>202369</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>202369</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>197965</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>197965</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>197965</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7570,72 +7570,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>200551</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>183860</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>222075</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>27,72%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>25,42%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>30,7%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>291</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>193578</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>175191</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>213686</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>174876</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>214060</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>28,13%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>25,46%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>31,06%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>200551</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>180200</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>220090</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>27,72%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>367262</t>
+          <t>367324</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>422653</t>
+          <t>422925</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,96%</t>
         </is>
       </c>
     </row>
@@ -7683,72 +7683,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>198209</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>179218</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>216562</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>27,4%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>24,77%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>29,94%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>302</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>199058</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>179875</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>218700</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>180567</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>219236</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>28,93%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>26,14%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>31,79%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>198209</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>180249</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>218865</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>27,4%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>366803</t>
+          <t>369875</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>425607</t>
+          <t>421711</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>29,88%</t>
         </is>
       </c>
     </row>
@@ -7796,72 +7796,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>324634</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>304775</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>346943</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>44,88%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>42,13%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>47,96%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>443</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>295425</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>273762</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>317065</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>272825</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>317407</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>42,94%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>39,79%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>46,08%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>324634</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>303314</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>346567</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>44,88%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>589484</t>
+          <t>589142</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>650447</t>
+          <t>650971</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,12%</t>
         </is>
       </c>
     </row>
@@ -7909,57 +7909,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1034</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>723394</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>723394</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>723394</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1036</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>688060</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>688060</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>688060</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1034</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>723394</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>723394</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>723394</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
